--- a/IV_6.5K_T1.xlsx
+++ b/IV_6.5K_T1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Queries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>

--- a/IV_6.5K_T1.xlsx
+++ b/IV_6.5K_T1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -3548,7 +3548,7 @@
         <v>-28.125</v>
       </c>
       <c r="J102">
-        <v>-3.7909999999999999E-2</v>
+        <v>-3.7920000000000002E-2</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -3562,7 +3562,7 @@
         <v>-29.6875</v>
       </c>
       <c r="D103">
-        <v>-4.002E-2</v>
+        <v>-4.0030000000000003E-2</v>
       </c>
       <c r="E103">
         <v>-29.6875</v>
@@ -3594,7 +3594,7 @@
         <v>-31.25</v>
       </c>
       <c r="D104">
-        <v>-4.2119999999999998E-2</v>
+        <v>-4.2110000000000002E-2</v>
       </c>
       <c r="E104">
         <v>-31.25</v>
@@ -3658,7 +3658,7 @@
         <v>-34.375</v>
       </c>
       <c r="D106">
-        <v>-4.6309999999999997E-2</v>
+        <v>-4.6300000000000001E-2</v>
       </c>
       <c r="E106">
         <v>-34.375</v>
@@ -3722,7 +3722,7 @@
         <v>-37.5</v>
       </c>
       <c r="D108">
-        <v>-5.0520000000000002E-2</v>
+        <v>-5.0509999999999999E-2</v>
       </c>
       <c r="E108">
         <v>-37.5</v>
@@ -3804,7 +3804,7 @@
         <v>-40.625</v>
       </c>
       <c r="J110">
-        <v>-5.4739999999999997E-2</v>
+        <v>-5.475E-2</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -3850,7 +3850,7 @@
         <v>-43.75</v>
       </c>
       <c r="D112">
-        <v>-5.8950000000000002E-2</v>
+        <v>-5.8959999999999999E-2</v>
       </c>
       <c r="E112">
         <v>-43.75</v>
@@ -3964,7 +3964,7 @@
         <v>-48.4375</v>
       </c>
       <c r="J115">
-        <v>-6.5269999999999995E-2</v>
+        <v>-6.5280000000000005E-2</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -4028,7 +4028,7 @@
         <v>-51.5625</v>
       </c>
       <c r="J117">
-        <v>-6.9540000000000005E-2</v>
+        <v>-6.9550000000000001E-2</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -4092,7 +4092,7 @@
         <v>-54.6875</v>
       </c>
       <c r="J119">
-        <v>-7.3770000000000002E-2</v>
+        <v>-7.3749999999999996E-2</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -4156,7 +4156,7 @@
         <v>-57.8125</v>
       </c>
       <c r="J121">
-        <v>-7.7979999999999994E-2</v>
+        <v>-7.7990000000000004E-2</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
